--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_43.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_43.xlsx
@@ -471,16 +471,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14200</v>
+        <v>4185</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Igor Moreira</t>
+          <t>Dra. Laura da Mata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,114 +489,114 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45103</v>
+        <v>45099</v>
       </c>
       <c r="G2" t="n">
-        <v>12318.16</v>
+        <v>11756.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61303</v>
+        <v>93592</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amanda Viana</t>
+          <t>Clarice da Rosa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45103</v>
+        <v>45089</v>
       </c>
       <c r="G3" t="n">
-        <v>3814.8</v>
+        <v>11571.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98144</v>
+        <v>14834</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lavínia Duarte</t>
+          <t>Ian Caldeira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45091</v>
+        <v>45088</v>
       </c>
       <c r="G4" t="n">
-        <v>8890.780000000001</v>
+        <v>11911.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13740</v>
+        <v>1403</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Davi Rocha</t>
+          <t>Larissa Pires</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45104</v>
+        <v>45079</v>
       </c>
       <c r="G5" t="n">
-        <v>8767.76</v>
+        <v>10709.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>39273</v>
+        <v>97992</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>João da Paz</t>
+          <t>Vitor Gabriel da Rosa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -605,109 +605,109 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45082</v>
+        <v>45104</v>
       </c>
       <c r="G6" t="n">
-        <v>4850.88</v>
+        <v>9956.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17092</v>
+        <v>50792</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sr. Pedro Lucas Dias</t>
+          <t>Laís Pereira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45105</v>
+        <v>45084</v>
       </c>
       <c r="G7" t="n">
-        <v>11044.65</v>
+        <v>5045.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7846</v>
+        <v>70306</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yuri Moraes</t>
+          <t>Pietro Costela</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45086</v>
+        <v>45088</v>
       </c>
       <c r="G8" t="n">
-        <v>12163.43</v>
+        <v>4840.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21470</v>
+        <v>85559</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ana Vitória da Rocha</t>
+          <t>Kamilly Fernandes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="G9" t="n">
-        <v>8663.549999999999</v>
+        <v>10597.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84781</v>
+        <v>5556</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ian Castro</t>
+          <t>Stella Gonçalves</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -717,46 +717,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45095</v>
+        <v>45089</v>
       </c>
       <c r="G10" t="n">
-        <v>8547.129999999999</v>
+        <v>10932.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29076</v>
+        <v>11295</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cecília Moreira</t>
+          <t>Luiz Fernando da Luz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45081</v>
+        <v>45096</v>
       </c>
       <c r="G11" t="n">
-        <v>11022.13</v>
+        <v>8306.799999999999</v>
       </c>
     </row>
   </sheetData>
